--- a/database/event/5519/event_5519_evp_summary.xlsx
+++ b/database/event/5519/event_5519_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.9152</v>
+        <v>9.855499999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3.8103</v>
+        <v>3.7873</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5842</v>
+        <v>3.4825</v>
       </c>
       <c r="E2" t="n">
-        <v>9.9152</v>
+        <v>9.855499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2255</v>
+        <v>3.1658</v>
       </c>
       <c r="G2" t="n">
         <v>6.6897</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2255</v>
+        <v>3.1658</v>
       </c>
       <c r="I2" t="n">
         <v>3.3013</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6894</v>
+        <v>6.6596</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5706</v>
+        <v>2.5592</v>
       </c>
       <c r="D3" t="n">
-        <v>2.281</v>
+        <v>2.2093</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6894</v>
+        <v>6.6596</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0023</v>
+        <v>1.9725</v>
       </c>
       <c r="G3" t="n">
         <v>4.6871</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0023</v>
+        <v>1.9725</v>
       </c>
       <c r="I3" t="n">
         <v>2.0398</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.5329</v>
+        <v>5.4899</v>
       </c>
       <c r="C4" t="n">
-        <v>2.1262</v>
+        <v>2.1097</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8138</v>
+        <v>1.7433</v>
       </c>
       <c r="E4" t="n">
-        <v>5.5329</v>
+        <v>5.4899</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8976</v>
+        <v>2.8546</v>
       </c>
       <c r="G4" t="n">
         <v>2.6353</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8976</v>
+        <v>2.8546</v>
       </c>
       <c r="I4" t="n">
         <v>2.9519</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8877</v>
+        <v>4.8494</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8783</v>
+        <v>1.8635</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5532</v>
+        <v>1.4881</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8877</v>
+        <v>4.8494</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0672</v>
+        <v>2.029</v>
       </c>
       <c r="G5" t="n">
         <v>2.8204</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0672</v>
+        <v>2.029</v>
       </c>
       <c r="I5" t="n">
         <v>2.1158</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7569</v>
+        <v>4.721</v>
       </c>
       <c r="C6" t="n">
-        <v>1.828</v>
+        <v>1.8142</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5003</v>
+        <v>1.4369</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7569</v>
+        <v>4.721</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4201</v>
+        <v>2.3841</v>
       </c>
       <c r="G6" t="n">
         <v>2.3368</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4201</v>
+        <v>2.3841</v>
       </c>
       <c r="I6" t="n">
         <v>2.4654</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.336</v>
+        <v>4.2869</v>
       </c>
       <c r="C7" t="n">
-        <v>1.6663</v>
+        <v>1.6474</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3303</v>
+        <v>1.264</v>
       </c>
       <c r="E7" t="n">
-        <v>4.336</v>
+        <v>4.2869</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3086</v>
+        <v>3.2595</v>
       </c>
       <c r="G7" t="n">
         <v>1.0274</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3086</v>
+        <v>3.2595</v>
       </c>
       <c r="I7" t="n">
         <v>3.3706</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7867</v>
+        <v>3.7531</v>
       </c>
       <c r="C8" t="n">
-        <v>1.4552</v>
+        <v>1.4423</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1084</v>
+        <v>1.0513</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7867</v>
+        <v>3.7531</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2643</v>
+        <v>2.2307</v>
       </c>
       <c r="G8" t="n">
         <v>1.5224</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2643</v>
+        <v>2.2307</v>
       </c>
       <c r="I8" t="n">
         <v>2.3068</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7712</v>
+        <v>3.7376</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4492</v>
+        <v>1.4363</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1021</v>
+        <v>1.0451</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7712</v>
+        <v>3.7376</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8146</v>
+        <v>1.781</v>
       </c>
       <c r="G9" t="n">
         <v>1.9566</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8146</v>
+        <v>1.781</v>
       </c>
       <c r="I9" t="n">
         <v>1.8572</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5658</v>
+        <v>3.5545</v>
       </c>
       <c r="C10" t="n">
-        <v>1.3703</v>
+        <v>1.3659</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0191</v>
+        <v>0.9722</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5658</v>
+        <v>3.5545</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6142</v>
+        <v>0.6028</v>
       </c>
       <c r="G10" t="n">
         <v>2.9517</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6142</v>
+        <v>0.6028</v>
       </c>
       <c r="I10" t="n">
         <v>0.6286</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1783</v>
+        <v>3.1282</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2214</v>
+        <v>1.2021</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8626</v>
+        <v>0.8024</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1783</v>
+        <v>3.1282</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3815</v>
+        <v>3.3314</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2032</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3815</v>
+        <v>3.3314</v>
       </c>
       <c r="I11" t="n">
         <v>3.4449</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0981</v>
+        <v>3.053</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1906</v>
+        <v>1.1732</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8302</v>
+        <v>0.7724</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0981</v>
+        <v>3.053</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0452</v>
+        <v>3.0001</v>
       </c>
       <c r="G12" t="n">
         <v>0.0529</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0452</v>
+        <v>3.0001</v>
       </c>
       <c r="I12" t="n">
         <v>3.1023</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.8615</v>
+        <v>2.8337</v>
       </c>
       <c r="C13" t="n">
-        <v>1.0996</v>
+        <v>1.0889</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7346</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8615</v>
+        <v>2.8337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.4722</v>
       </c>
       <c r="G13" t="n">
         <v>1.3615</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>1.4722</v>
       </c>
       <c r="I13" t="n">
         <v>1.5352</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7295</v>
+        <v>2.6904</v>
       </c>
       <c r="C14" t="n">
-        <v>1.0489</v>
+        <v>1.0339</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6813</v>
+        <v>0.6279</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7295</v>
+        <v>2.6904</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6348</v>
+        <v>2.5957</v>
       </c>
       <c r="G14" t="n">
         <v>0.09470000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6348</v>
+        <v>2.5957</v>
       </c>
       <c r="I14" t="n">
         <v>2.6842</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7214</v>
+        <v>2.6815</v>
       </c>
       <c r="C15" t="n">
-        <v>1.0458</v>
+        <v>1.0305</v>
       </c>
       <c r="D15" t="n">
-        <v>0.678</v>
+        <v>0.6244</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7214</v>
+        <v>2.6815</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3141</v>
+        <v>2.0658</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5927</v>
+        <v>0.6157</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3141</v>
+        <v>2.0658</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3762</v>
+        <v>2.1363</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5927</v>
+        <v>0.6157</v>
       </c>
       <c r="K15" t="n">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="L15" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7835</v>
+        <v>2.752</v>
       </c>
       <c r="N15" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7127</v>
+        <v>2.6722</v>
       </c>
       <c r="C16" t="n">
-        <v>1.0424</v>
+        <v>1.0269</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6745</v>
+        <v>0.6207</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7127</v>
+        <v>2.6722</v>
       </c>
       <c r="F16" t="n">
-        <v>2.097</v>
+        <v>3.2649</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6157</v>
+        <v>-0.5927</v>
       </c>
       <c r="H16" t="n">
-        <v>2.097</v>
+        <v>3.2649</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1363</v>
+        <v>3.3762</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6157</v>
+        <v>-0.5927</v>
       </c>
       <c r="K16" t="n">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="M16" t="n">
-        <v>2.752</v>
+        <v>2.7835</v>
       </c>
       <c r="N16" t="n">
-        <v>231</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.6655</v>
+        <v>2.6465</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0243</v>
+        <v>1.017</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6554</v>
+        <v>0.6105</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6655</v>
+        <v>2.6465</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2775</v>
+        <v>1.2585</v>
       </c>
       <c r="G17" t="n">
         <v>1.388</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2775</v>
+        <v>1.2585</v>
       </c>
       <c r="I17" t="n">
         <v>1.3014</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5187</v>
+        <v>2.4893</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9679</v>
+        <v>0.9566</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5961</v>
+        <v>0.5478</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5187</v>
+        <v>2.4893</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2332</v>
+        <v>0.7671</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7145</v>
+        <v>1.7222</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2332</v>
+        <v>0.7671</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2938</v>
+        <v>0.7933</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7145</v>
+        <v>1.7222</v>
       </c>
       <c r="K18" t="n">
-        <v>213</v>
+        <v>135</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5793</v>
+        <v>2.5155</v>
       </c>
       <c r="N18" t="n">
-        <v>259</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.5009</v>
+        <v>2.4707</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9611</v>
+        <v>0.9495</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5889</v>
+        <v>0.5404</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5009</v>
+        <v>2.4707</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7786999999999999</v>
+        <v>3.1852</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7222</v>
+        <v>-0.7145</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7786999999999999</v>
+        <v>3.1852</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7933</v>
+        <v>3.2938</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7222</v>
+        <v>-0.7145</v>
       </c>
       <c r="K19" t="n">
-        <v>135</v>
+        <v>213</v>
       </c>
       <c r="L19" t="n">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>2.5155</v>
+        <v>2.5793</v>
       </c>
       <c r="N19" t="n">
-        <v>296</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3586</v>
+        <v>2.3323</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9064</v>
+        <v>0.8963</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5315</v>
+        <v>0.4853</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3586</v>
+        <v>2.3323</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3586</v>
+        <v>2.3323</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3586</v>
+        <v>2.3323</v>
       </c>
       <c r="I20" t="n">
         <v>2.3917</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2744</v>
+        <v>2.2359</v>
       </c>
       <c r="C21" t="n">
-        <v>0.874</v>
+        <v>0.8592</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4974</v>
+        <v>0.4469</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2744</v>
+        <v>2.2359</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6009</v>
+        <v>2.5624</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3265</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6009</v>
+        <v>2.5624</v>
       </c>
       <c r="I21" t="n">
         <v>2.6497</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.1647</v>
+        <v>2.1185</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8319</v>
+        <v>0.8141</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4531</v>
+        <v>0.4001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1647</v>
+        <v>2.1185</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1136</v>
+        <v>3.0674</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9489</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1136</v>
+        <v>3.0674</v>
       </c>
       <c r="I22" t="n">
         <v>3.172</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.1156</v>
+        <v>2.0811</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7997</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4333</v>
+        <v>0.3852</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1156</v>
+        <v>2.0811</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3258</v>
+        <v>2.2913</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2102</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3258</v>
+        <v>2.2913</v>
       </c>
       <c r="I23" t="n">
         <v>2.3694</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.8564</v>
+        <v>1.833</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7134</v>
+        <v>0.7044</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3286</v>
+        <v>0.2864</v>
       </c>
       <c r="E24" t="n">
-        <v>1.8564</v>
+        <v>1.833</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5756</v>
+        <v>1.5522</v>
       </c>
       <c r="G24" t="n">
         <v>0.2808</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5756</v>
+        <v>1.5522</v>
       </c>
       <c r="I24" t="n">
         <v>1.6052</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5623</v>
+        <v>1.5339</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6004</v>
+        <v>0.5895</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2098</v>
+        <v>0.1672</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5623</v>
+        <v>1.5339</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9135</v>
+        <v>1.8851</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3512</v>
       </c>
       <c r="H25" t="n">
-        <v>1.9135</v>
+        <v>1.8851</v>
       </c>
       <c r="I25" t="n">
         <v>1.9494</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3825</v>
+        <v>1.3722</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5313</v>
+        <v>0.5273</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1371</v>
+        <v>0.1028</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3825</v>
+        <v>1.3722</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3825</v>
+        <v>1.3722</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3825</v>
+        <v>1.3722</v>
       </c>
       <c r="I26" t="n">
         <v>1.3954</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.3245</v>
+        <v>1.2942</v>
       </c>
       <c r="C27" t="n">
-        <v>0.509</v>
+        <v>0.4973</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1137</v>
+        <v>0.0717</v>
       </c>
       <c r="E27" t="n">
-        <v>1.3245</v>
+        <v>1.2942</v>
       </c>
       <c r="F27" t="n">
-        <v>2.041</v>
+        <v>2.0107</v>
       </c>
       <c r="G27" t="n">
         <v>-0.7165</v>
       </c>
       <c r="H27" t="n">
-        <v>2.041</v>
+        <v>2.0107</v>
       </c>
       <c r="I27" t="n">
         <v>2.0793</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2106</v>
+        <v>1.1971</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4652</v>
+        <v>0.46</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0677</v>
+        <v>0.033</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2106</v>
+        <v>1.1971</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2106</v>
+        <v>1.1971</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2106</v>
+        <v>1.1971</v>
       </c>
       <c r="I28" t="n">
         <v>1.2276</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2013</v>
+        <v>1.1754</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4616</v>
+        <v>0.4517</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0639</v>
+        <v>0.0244</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2013</v>
+        <v>1.1754</v>
       </c>
       <c r="F29" t="n">
-        <v>1.7422</v>
+        <v>1.7163</v>
       </c>
       <c r="G29" t="n">
         <v>-0.5409</v>
       </c>
       <c r="H29" t="n">
-        <v>1.7422</v>
+        <v>1.7163</v>
       </c>
       <c r="I29" t="n">
         <v>1.7748</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1391</v>
+        <v>1.1264</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4377</v>
+        <v>0.4329</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0388</v>
+        <v>0.0048</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1391</v>
+        <v>1.1264</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1391</v>
+        <v>1.1264</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1391</v>
+        <v>1.1264</v>
       </c>
       <c r="I30" t="n">
         <v>1.1551</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.009</v>
+        <v>1.0228</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3877</v>
+        <v>0.393</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.0137</v>
+        <v>-0.0364</v>
       </c>
       <c r="E31" t="n">
-        <v>1.009</v>
+        <v>1.0228</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7456</v>
+        <v>-0.7318</v>
       </c>
       <c r="G31" t="n">
         <v>1.7546</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7456</v>
+        <v>-0.7318</v>
       </c>
       <c r="I31" t="n">
         <v>-0.7631</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9608</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3692</v>
+        <v>0.3678</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.0332</v>
+        <v>-0.0626</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9608</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9608</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9608</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>0.9653</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="C33" t="n">
-        <v>0.355</v>
+        <v>0.3537</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0481</v>
+        <v>-0.0772</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9205</v>
       </c>
       <c r="I33" t="n">
         <v>0.9282</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3508</v>
+        <v>0.3482</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0526</v>
+        <v>-0.083</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="I34" t="n">
         <v>0.9213</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8583</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3298</v>
+        <v>0.3225</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0746</v>
+        <v>-0.1096</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8583</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2858</v>
+        <v>1.2667</v>
       </c>
       <c r="G35" t="n">
         <v>-0.4275</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2858</v>
+        <v>1.2667</v>
       </c>
       <c r="I35" t="n">
         <v>1.3099</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6785</v>
+        <v>0.676</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2607</v>
+        <v>0.2598</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1473</v>
+        <v>-0.1746</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6785</v>
+        <v>0.676</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6785</v>
+        <v>0.676</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6785</v>
+        <v>0.676</v>
       </c>
       <c r="I36" t="n">
         <v>0.6817</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6545</v>
+        <v>0.6496</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2515</v>
+        <v>0.2496</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.157</v>
+        <v>-0.1851</v>
       </c>
       <c r="E37" t="n">
-        <v>0.6545</v>
+        <v>0.6496</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6545</v>
+        <v>0.6496</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6545</v>
+        <v>0.6496</v>
       </c>
       <c r="I37" t="n">
         <v>0.6606</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.3758</v>
+        <v>0.373</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1444</v>
+        <v>0.1433</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.2695</v>
+        <v>-0.2953</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3758</v>
+        <v>0.373</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3758</v>
+        <v>0.373</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3758</v>
+        <v>0.373</v>
       </c>
       <c r="I38" t="n">
         <v>0.3793</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.3454</v>
+        <v>0.3441</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1327</v>
+        <v>0.1322</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2818</v>
+        <v>-0.3068</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3454</v>
+        <v>0.3441</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3454</v>
+        <v>0.3441</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3454</v>
+        <v>0.3441</v>
       </c>
       <c r="I39" t="n">
         <v>0.347</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.3136</v>
+        <v>0.3112</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1205</v>
+        <v>0.1196</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2947</v>
+        <v>-0.3199</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3136</v>
+        <v>0.3112</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3136</v>
+        <v>0.3112</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3136</v>
+        <v>0.3112</v>
       </c>
       <c r="I40" t="n">
         <v>0.3165</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2397</v>
+        <v>0.2379</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0921</v>
+        <v>0.0914</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3245</v>
+        <v>-0.3491</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2397</v>
+        <v>0.2379</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2397</v>
+        <v>0.2379</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2397</v>
+        <v>0.2379</v>
       </c>
       <c r="I41" t="n">
         <v>0.2419</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1934</v>
+        <v>0.1773</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0743</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3432</v>
+        <v>-0.3733</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1934</v>
+        <v>0.1773</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0847</v>
+        <v>1.0686</v>
       </c>
       <c r="G42" t="n">
         <v>-0.8913</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0847</v>
+        <v>1.0686</v>
       </c>
       <c r="I42" t="n">
         <v>1.105</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1379</v>
+        <v>0.1369</v>
       </c>
       <c r="C43" t="n">
-        <v>0.053</v>
+        <v>0.0526</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3657</v>
+        <v>-0.3894</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1379</v>
+        <v>0.1369</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1379</v>
+        <v>0.1369</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1379</v>
+        <v>0.1369</v>
       </c>
       <c r="I43" t="n">
         <v>0.1392</v>
@@ -2424,93 +2424,93 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1071</v>
+        <v>0.1156</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0412</v>
+        <v>0.0444</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3781</v>
+        <v>-0.3979</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1071</v>
+        <v>0.1156</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8123</v>
+        <v>-1.4087</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.7052</v>
+        <v>1.5243</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8123</v>
+        <v>-1.4087</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8275</v>
+        <v>-1.469</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.7052</v>
+        <v>1.5243</v>
       </c>
       <c r="K44" t="n">
-        <v>135</v>
+        <v>237</v>
       </c>
       <c r="L44" t="n">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1223</v>
+        <v>0.0552999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.089</v>
+        <v>0.095</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0342</v>
+        <v>0.0365</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3854</v>
+        <v>-0.4061</v>
       </c>
       <c r="E45" t="n">
-        <v>0.089</v>
+        <v>0.095</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.4353</v>
+        <v>0.8002</v>
       </c>
       <c r="G45" t="n">
-        <v>1.5243</v>
+        <v>-0.7052</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.4353</v>
+        <v>0.8002</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.469</v>
+        <v>0.8275</v>
       </c>
       <c r="J45" t="n">
-        <v>1.5243</v>
+        <v>-0.7052</v>
       </c>
       <c r="K45" t="n">
-        <v>237</v>
+        <v>135</v>
       </c>
       <c r="L45" t="n">
-        <v>166</v>
+        <v>250</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0552999999999999</v>
+        <v>0.1223</v>
       </c>
       <c r="N45" t="n">
-        <v>403</v>
+        <v>385</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0489</v>
+        <v>0.0487</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0188</v>
+        <v>0.0187</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4016</v>
+        <v>-0.4245</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0489</v>
+        <v>0.0487</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0489</v>
+        <v>0.0487</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0489</v>
+        <v>0.0487</v>
       </c>
       <c r="I46" t="n">
         <v>0.0491</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.0176</v>
+        <v>0.0174</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4143</v>
+        <v>-0.437</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0176</v>
+        <v>0.0174</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0176</v>
+        <v>0.0174</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0176</v>
+        <v>0.0174</v>
       </c>
       <c r="I47" t="n">
         <v>0.0179</v>
@@ -2618,7 +2618,7 @@
         <v>0.0051</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4159</v>
+        <v>-0.4386</v>
       </c>
       <c r="E48" t="n">
         <v>0.0134</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0103</v>
+        <v>-0.0249</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.004</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4255</v>
+        <v>-0.4538</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0103</v>
+        <v>-0.0249</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9897</v>
+        <v>0.9751</v>
       </c>
       <c r="G49" t="n">
         <v>-1</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9897</v>
+        <v>0.9751</v>
       </c>
       <c r="I49" t="n">
         <v>1.0083</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0142</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4363</v>
+        <v>-0.4587</v>
       </c>
       <c r="E50" t="n">
         <v>-0.037</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.0595</v>
+        <v>-0.0588</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0229</v>
+        <v>-0.0226</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4454</v>
+        <v>-0.4673</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.0595</v>
+        <v>-0.0588</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0595</v>
+        <v>-0.0588</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0595</v>
+        <v>-0.0588</v>
       </c>
       <c r="I51" t="n">
         <v>-0.0603</v>
@@ -2792,93 +2792,93 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1598</v>
+        <v>-0.1592</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0614</v>
+        <v>-0.0612</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4859</v>
+        <v>-0.5073</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1598</v>
+        <v>-0.1592</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8687</v>
+        <v>-0.1592</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.0285</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8687</v>
+        <v>-0.1592</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8891</v>
+        <v>-0.1633</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.0285</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>192</v>
+        <v>231</v>
       </c>
       <c r="L52" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1394</v>
+        <v>-0.1633</v>
       </c>
       <c r="N52" t="n">
-        <v>328</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.161</v>
+        <v>-0.1759</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0619</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4864</v>
+        <v>-0.514</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.161</v>
+        <v>-0.1759</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.161</v>
+        <v>0.8526</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-1.0285</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.161</v>
+        <v>0.8526</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1633</v>
+        <v>0.8891</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-1.0285</v>
       </c>
       <c r="K53" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1633</v>
+        <v>-0.1394</v>
       </c>
       <c r="N53" t="n">
-        <v>231</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54">
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.1824</v>
+        <v>-0.1817</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0701</v>
+        <v>-0.0698</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.495</v>
+        <v>-0.5163</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.1824</v>
+        <v>-0.1817</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.1824</v>
+        <v>-0.1817</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.1824</v>
+        <v>-0.1817</v>
       </c>
       <c r="I54" t="n">
         <v>-0.1832</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2397</v>
+        <v>-0.2371</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0921</v>
+        <v>-0.0911</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5182</v>
+        <v>-0.5384</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2397</v>
+        <v>-0.2371</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2397</v>
+        <v>-0.2371</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2397</v>
+        <v>-0.2371</v>
       </c>
       <c r="I55" t="n">
         <v>-0.2431</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2601</v>
+        <v>-0.2591</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5264</v>
+        <v>-0.5471</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2601</v>
+        <v>-0.2591</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2601</v>
+        <v>-0.2591</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2601</v>
+        <v>-0.2591</v>
       </c>
       <c r="I56" t="n">
         <v>-0.2613</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.2723</v>
+        <v>-0.2605</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1046</v>
+        <v>-0.1001</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5314</v>
+        <v>-0.5477</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2723</v>
+        <v>-0.2605</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6409</v>
+        <v>-0.6291</v>
       </c>
       <c r="G57" t="n">
         <v>0.3686</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.6409</v>
+        <v>-0.6291</v>
       </c>
       <c r="I57" t="n">
         <v>-0.656</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3224</v>
+        <v>-0.3203</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.1239</v>
+        <v>-0.1231</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5516</v>
+        <v>-0.5715</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3224</v>
+        <v>-0.3203</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1358</v>
+        <v>-0.1337</v>
       </c>
       <c r="G58" t="n">
         <v>-0.1866</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1358</v>
+        <v>-0.1337</v>
       </c>
       <c r="I58" t="n">
         <v>-0.1383</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1655</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5954</v>
+        <v>-0.6155</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4308</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4718</v>
+        <v>-0.4665</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.1813</v>
+        <v>-0.1793</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.612</v>
+        <v>-0.6298</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4718</v>
+        <v>-0.4665</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4718</v>
+        <v>-0.4665</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4718</v>
+        <v>-0.4665</v>
       </c>
       <c r="I60" t="n">
         <v>-0.4784</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5208</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2016</v>
+        <v>-0.2001</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6333</v>
+        <v>-0.6514</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5208</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5208</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5208</v>
       </c>
       <c r="I61" t="n">
         <v>-0.5296</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2446</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6785</v>
+        <v>-0.6975</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6366000000000001</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6904</v>
+        <v>-0.6878</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.2653</v>
+        <v>-0.2643</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7003</v>
+        <v>-0.7179</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6904</v>
+        <v>-0.6878</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6904</v>
+        <v>-0.6878</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6904</v>
+        <v>-0.6878</v>
       </c>
       <c r="I63" t="n">
         <v>-0.6936</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7027</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.27</v>
+        <v>-0.269</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7052</v>
+        <v>-0.7228</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7027</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7027</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7027</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>-0.706</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8368</v>
+        <v>-0.8337</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3216</v>
+        <v>-0.3204</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7594</v>
+        <v>-0.7761</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8368</v>
+        <v>-0.8337</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8368</v>
+        <v>-0.8337</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8368</v>
+        <v>-0.8337</v>
       </c>
       <c r="I65" t="n">
         <v>-0.8407</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8671</v>
+        <v>-0.8638</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3332</v>
+        <v>-0.3319</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.788</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8671</v>
+        <v>-0.8638</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8671</v>
+        <v>-0.8638</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8671</v>
+        <v>-0.8638</v>
       </c>
       <c r="I66" t="n">
         <v>-0.8711</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8776</v>
+        <v>-0.8678</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3372</v>
+        <v>-0.3335</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7759</v>
+        <v>-0.7896</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8776</v>
+        <v>-0.8678</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8776</v>
+        <v>-0.8678</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8776</v>
+        <v>-0.8678</v>
       </c>
       <c r="I67" t="n">
         <v>-0.8899</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8807</v>
+        <v>-0.8774</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3384</v>
+        <v>-0.3372</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7771</v>
+        <v>-0.7935</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8807</v>
+        <v>-0.8774</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8807</v>
+        <v>-0.8774</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8807</v>
+        <v>-0.8774</v>
       </c>
       <c r="I68" t="n">
         <v>-0.8848</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8953</v>
+        <v>-0.8887</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.344</v>
+        <v>-0.3415</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.783</v>
+        <v>-0.798</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8953</v>
+        <v>-0.8887</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8953</v>
+        <v>-0.8887</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8953</v>
+        <v>-0.8887</v>
       </c>
       <c r="I69" t="n">
         <v>-0.9036999999999999</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9099</v>
+        <v>-0.8998</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3497</v>
+        <v>-0.3458</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7889</v>
+        <v>-0.8024</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9099</v>
+        <v>-0.8998</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9099</v>
+        <v>-0.8998</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9099</v>
+        <v>-0.8998</v>
       </c>
       <c r="I70" t="n">
         <v>-0.9227</v>
@@ -3666,93 +3666,93 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9391</v>
+        <v>-0.9388</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3609</v>
+        <v>-0.3608</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8007</v>
+        <v>-0.8179</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9391</v>
+        <v>-0.9388</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5683</v>
+        <v>-0.0655</v>
       </c>
       <c r="G71" t="n">
-        <v>-1.5074</v>
+        <v>-0.8733</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5683</v>
+        <v>-0.0655</v>
       </c>
       <c r="I71" t="n">
-        <v>0.579</v>
+        <v>-0.0677</v>
       </c>
       <c r="J71" t="n">
-        <v>-1.5074</v>
+        <v>-0.8733</v>
       </c>
       <c r="K71" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L71" t="n">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9284000000000001</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="N71" t="n">
-        <v>366</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9398</v>
+        <v>-0.9475</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3612</v>
+        <v>-0.3641</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.801</v>
+        <v>-0.8214</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9398</v>
+        <v>-0.9475</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.0665</v>
+        <v>0.5599</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.8733</v>
+        <v>-1.5074</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.0665</v>
+        <v>0.5599</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.0677</v>
+        <v>0.579</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.8733</v>
+        <v>-1.5074</v>
       </c>
       <c r="K72" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L72" t="n">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9284000000000001</v>
       </c>
       <c r="N72" t="n">
-        <v>214</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73">
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0123</v>
+        <v>-1.0085</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.389</v>
+        <v>-0.3876</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8303</v>
+        <v>-0.8457</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0123</v>
+        <v>-1.0085</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0123</v>
+        <v>-1.0085</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0123</v>
+        <v>-1.0085</v>
       </c>
       <c r="I73" t="n">
         <v>-1.017</v>
@@ -3814,7 +3814,7 @@
         <v>-0.4596</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9045</v>
+        <v>-0.9204</v>
       </c>
       <c r="E74" t="n">
         <v>-1.196</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2123</v>
+        <v>-1.1988</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4659</v>
+        <v>-0.4607</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9111</v>
+        <v>-0.9215</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2123</v>
+        <v>-1.1988</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2123</v>
+        <v>-1.1988</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2123</v>
+        <v>-1.1988</v>
       </c>
       <c r="I75" t="n">
         <v>-1.2293</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2287</v>
+        <v>-1.2241</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.4722</v>
+        <v>-0.4704</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9177</v>
+        <v>-0.9316</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2287</v>
+        <v>-1.2241</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.2287</v>
+        <v>-1.2241</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.2287</v>
+        <v>-1.2241</v>
       </c>
       <c r="I76" t="n">
         <v>-1.2344</v>
@@ -3952,7 +3952,7 @@
         <v>-0.4917</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9383</v>
+        <v>-0.9537</v>
       </c>
       <c r="E77" t="n">
         <v>-1.2795</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5367</v>
+        <v>-1.5287</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.5905</v>
+        <v>-0.5875</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0422</v>
+        <v>-1.0529</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5367</v>
+        <v>-1.5287</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.5367</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="G78" t="n">
         <v>-1</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.5367</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="I78" t="n">
         <v>-0.5468</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9525</v>
+        <v>-1.9365</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7503</v>
+        <v>-0.7442</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2101</v>
+        <v>-1.2154</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9525</v>
+        <v>-1.9365</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.074</v>
+        <v>-1.058</v>
       </c>
       <c r="G79" t="n">
         <v>-0.8784999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.074</v>
+        <v>-1.058</v>
       </c>
       <c r="I79" t="n">
         <v>-1.0941</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.1489</v>
+        <v>-2.1423</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8258</v>
+        <v>-0.8233</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2895</v>
+        <v>-1.2974</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.1489</v>
+        <v>-2.1423</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.36</v>
+        <v>-0.3534</v>
       </c>
       <c r="G80" t="n">
         <v>-1.7889</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.36</v>
+        <v>-0.3534</v>
       </c>
       <c r="I80" t="n">
         <v>-0.3685</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1755</v>
+        <v>-2.1593</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.836</v>
+        <v>-0.8298</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3002</v>
+        <v>-1.3042</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1755</v>
+        <v>-2.1593</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1755</v>
+        <v>-2.1593</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1755</v>
+        <v>-2.1593</v>
       </c>
       <c r="I81" t="n">
         <v>-2.1958</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.5242</v>
+        <v>-2.496</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.97</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.4411</v>
+        <v>-1.4383</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.5242</v>
+        <v>-2.496</v>
       </c>
       <c r="F82" t="n">
-        <v>-2.5242</v>
+        <v>-2.496</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.5242</v>
+        <v>-2.496</v>
       </c>
       <c r="I82" t="n">
         <v>-2.5596</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-2.8545</v>
+        <v>-2.827</v>
       </c>
       <c r="C83" t="n">
-        <v>-1.0969</v>
+        <v>-1.0864</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.5745</v>
+        <v>-1.5702</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.8545</v>
+        <v>-2.827</v>
       </c>
       <c r="F83" t="n">
-        <v>-1.8545</v>
+        <v>-1.827</v>
       </c>
       <c r="G83" t="n">
         <v>-1</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.8545</v>
+        <v>-1.827</v>
       </c>
       <c r="I83" t="n">
         <v>-1.8893</v>
